--- a/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
+++ b/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\Cattle-Slurry 2025-10-28\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-28-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B749A9-66EF-470D-A60F-5B8B464E9C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B918CD5A-03A6-4C98-8444-05775806C3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -607,7 +607,8 @@
     <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">

--- a/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
+++ b/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-28-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B918CD5A-03A6-4C98-8444-05775806C3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAB7481-C114-4C83-8E13-5F0B5714BEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>Comments</t>
   </si>
@@ -222,6 +222,18 @@
   </si>
   <si>
     <t>Δt [h]</t>
+  </si>
+  <si>
+    <t>[L]</t>
+  </si>
+  <si>
+    <t>chamber volume</t>
+  </si>
+  <si>
+    <t>AER [1/s]</t>
+  </si>
+  <si>
+    <t>AER [1/min]</t>
   </si>
 </sst>
 </file>
@@ -597,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" bestFit="1" customWidth="1"/>
@@ -609,9 +621,11 @@
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,19 +654,25 @@
         <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45958</v>
       </c>
@@ -678,24 +698,32 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="J2">
-        <f>(F2^0.5)*$M$2</f>
+        <f>(F2^0.5)*$P$2</f>
         <v>34.36277055186325</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2">
+        <f>J2/$P$3</f>
+        <v>0.22908513701242167</v>
+      </c>
+      <c r="L2" s="4">
+        <f>K2*60</f>
+        <v>13.745108220745299</v>
+      </c>
+      <c r="N2" s="3">
         <f>I2-G2</f>
         <v>1.5277777777777779E-2</v>
       </c>
-      <c r="M2">
+      <c r="P2">
         <v>3</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Q2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -721,8 +749,18 @@
       <c r="I3" s="3">
         <v>0.45694444444444443</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <f>0.15 *1000</f>
+        <v>150</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -749,11 +787,19 @@
         <v>0.46250000000000002</v>
       </c>
       <c r="J4">
-        <f>(F4^0.5)*$M$2</f>
+        <f>(F4^0.5)*$P$2</f>
         <v>34.36277055186325</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <f>J4/$P$3</f>
+        <v>0.22908513701242167</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" ref="L3:L13" si="1">K4*60</f>
+        <v>13.745108220745299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -780,7 +826,7 @@
         <v>0.468055555555556</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -807,11 +853,19 @@
         <v>0.47361111111111098</v>
       </c>
       <c r="J6">
-        <f>(F6^0.5)*$M$2</f>
+        <f>(F6^0.5)*$P$2</f>
         <v>33.634803403617511</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K6">
+        <f>J6/$P$3</f>
+        <v>0.22423202269078341</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="1"/>
+        <v>13.453921361447005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>12</v>
       </c>
@@ -835,11 +889,19 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="J7">
-        <f>(F7^0.5)*$M$2</f>
+        <f>(F7^0.5)*$P$2</f>
         <v>34.139420030223128</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <f>J7/$P$3</f>
+        <v>0.22759613353482086</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" si="1"/>
+        <v>13.655768012089252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -866,11 +928,19 @@
         <v>0.484722222222222</v>
       </c>
       <c r="J8">
-        <f>(F8^0.5)*$M$2</f>
+        <f>(F8^0.5)*$P$2</f>
         <v>33.848190498164001</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K8">
+        <f>J8/$P$3</f>
+        <v>0.22565460332109336</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" si="1"/>
+        <v>13.539276199265601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -897,11 +967,19 @@
         <v>0.49027777777777798</v>
       </c>
       <c r="J9">
-        <f>(F9^0.5)*$M$2</f>
+        <f>(F9^0.5)*$P$2</f>
         <v>34.415112959279966</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <f>J9/$P$3</f>
+        <v>0.22943408639519977</v>
+      </c>
+      <c r="L9" s="4">
+        <f t="shared" si="1"/>
+        <v>13.766045183711986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -928,11 +1006,19 @@
         <v>0.49583333333333302</v>
       </c>
       <c r="J10">
-        <f>(F10^0.5)*$M$2</f>
+        <f>(F10^0.5)*$P$2</f>
         <v>34.375863625514924</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <f>J10/$P$3</f>
+        <v>0.2291724241700995</v>
+      </c>
+      <c r="L10" s="4">
+        <f t="shared" si="1"/>
+        <v>13.75034545020597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C11">
         <v>16</v>
       </c>
@@ -956,7 +1042,7 @@
         <v>0.50138888888888899</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>17</v>
       </c>
@@ -980,11 +1066,19 @@
         <v>0.50694444444444398</v>
       </c>
       <c r="J12">
-        <f>(F12^0.5)*$M$2</f>
+        <f>(F12^0.5)*$P$2</f>
         <v>34.139420030223128</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <f>J12/$P$3</f>
+        <v>0.22759613353482086</v>
+      </c>
+      <c r="L12" s="4">
+        <f t="shared" si="1"/>
+        <v>13.655768012089252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>18</v>
       </c>
@@ -1008,8 +1102,16 @@
         <v>0.51249999999999996</v>
       </c>
       <c r="J13">
-        <f>(F13^0.5)*$M$2</f>
+        <f>(F13^0.5)*$P$2</f>
         <v>33.621421742692561</v>
+      </c>
+      <c r="K13">
+        <f>J13/$P$3</f>
+        <v>0.22414281161795041</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="1"/>
+        <v>13.448568697077025</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
+++ b/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-28-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAB7481-C114-4C83-8E13-5F0B5714BEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5951B5F-3F3A-4D57-8C2B-5438BDDEBA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -283,12 +283,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -303,12 +309,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -733,20 +742,20 @@
       <c r="D3">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="6">
         <v>0.44166666666666665</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="7">
         <f>H2+(8/60)</f>
         <v>0.13333333333333333</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="6">
         <v>0.45694444444444443</v>
       </c>
       <c r="P3">
@@ -795,7 +804,7 @@
         <v>0.22908513701242167</v>
       </c>
       <c r="L4" s="4">
-        <f t="shared" ref="L3:L13" si="1">K4*60</f>
+        <f t="shared" ref="L4:L13" si="1">K4*60</f>
         <v>13.745108220745299</v>
       </c>
     </row>
@@ -809,20 +818,20 @@
       <c r="D5">
         <v>7</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="6">
         <v>0.452777777777778</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="7">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="6">
         <v>0.468055555555556</v>
       </c>
     </row>
@@ -1025,20 +1034,20 @@
       <c r="D11">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="6">
         <v>0.48611111111111099</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="7">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="6">
         <v>0.50138888888888899</v>
       </c>
     </row>

--- a/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
+++ b/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-28-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5951B5F-3F3A-4D57-8C2B-5438BDDEBA5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A815C21-3728-4049-9809-887D2C051D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>Comments</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>AER [1/min]</t>
+  </si>
+  <si>
+    <t>Wi</t>
   </si>
 </sst>
 </file>
@@ -703,8 +706,8 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="3">
-        <v>0.4513888888888889</v>
+      <c r="I2" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="J2">
         <f>(F2^0.5)*$P$2</f>
@@ -718,9 +721,9 @@
         <f>K2*60</f>
         <v>13.745108220745299</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="3" t="e">
         <f>I2-G2</f>
-        <v>1.5277777777777779E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P2">
         <v>3</v>

--- a/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
+++ b/Field-trails/2025-10-28-cattle-slurry/DFC overview cattle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\2025-10-28-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A815C21-3728-4049-9809-887D2C051D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FBB90D-F044-4D6C-AAB1-2CBA6C7A16BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     Piccaro-time, deviation from actual time</t>
       </text>
     </comment>
-    <comment ref="C5" authorId="1" shapeId="0" xr:uid="{BAE6371E-30DD-4536-96D0-2B28705CE14C}">
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{BAE6371E-30DD-4536-96D0-2B28705CE14C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>Comments</t>
   </si>
@@ -235,9 +235,6 @@
   <si>
     <t>AER [1/min]</t>
   </si>
-  <si>
-    <t>Wi</t>
-  </si>
 </sst>
 </file>
 
@@ -286,7 +283,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,6 +293,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -321,6 +324,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -610,7 +614,7 @@
   <threadedComment ref="G1" dT="2025-10-29T18:17:41.60" personId="{22A5EB89-AB59-4A7F-87CF-6DED706BEC2F}" id="{FDF15974-591A-45F1-80AF-CE85306F16C3}">
     <text>Piccaro-time, deviation from actual time</text>
   </threadedComment>
-  <threadedComment ref="C5" dT="2025-10-29T18:20:51.49" personId="{22A5EB89-AB59-4A7F-87CF-6DED706BEC2F}" id="{BAE6371E-30DD-4536-96D0-2B28705CE14C}">
+  <threadedComment ref="D5" dT="2025-10-29T18:20:51.49" personId="{22A5EB89-AB59-4A7F-87CF-6DED706BEC2F}" id="{BAE6371E-30DD-4536-96D0-2B28705CE14C}">
     <text>Valved-error made it so valves &gt;10 were not meassured before 16:55 - it was suck measureing 9 for this duration</text>
   </threadedComment>
   <threadedComment ref="F10" dT="2025-10-29T18:15:15.77" personId="{22A5EB89-AB59-4A7F-87CF-6DED706BEC2F}" id="{17A9D219-9D9F-4B27-86C1-09351BB3D7DF}">
@@ -625,8 +629,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -635,6 +638,7 @@
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -642,10 +646,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -688,7 +692,7 @@
       <c r="A2" s="2">
         <v>45958</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>4</v>
       </c>
       <c r="D2">
@@ -706,8 +710,9 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>31</v>
+      <c r="I2" s="3">
+        <f>G2+N2</f>
+        <v>0.4513888888888889</v>
       </c>
       <c r="J2">
         <f>(F2^0.5)*$P$2</f>
@@ -721,9 +726,9 @@
         <f>K2*60</f>
         <v>13.745108220745299</v>
       </c>
-      <c r="N2" s="3" t="e">
-        <f>I2-G2</f>
-        <v>#VALUE!</v>
+      <c r="N2" s="3">
+        <f>I3-G3</f>
+        <v>1.5277777777777779E-2</v>
       </c>
       <c r="P2">
         <v>3</v>
@@ -739,11 +744,11 @@
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>5</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
@@ -776,11 +781,11 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
+        <v>7</v>
+      </c>
+      <c r="D4">
         <v>8</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -815,11 +820,11 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
+        <v>7</v>
+      </c>
+      <c r="D5">
         <v>9</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>8</v>
@@ -842,11 +847,11 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
+        <v>9</v>
+      </c>
+      <c r="D6">
         <v>11</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -878,11 +883,11 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C7">
+      <c r="C7" s="8">
+        <v>10</v>
+      </c>
+      <c r="D7">
         <v>12</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -917,11 +922,11 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
+        <v>11</v>
+      </c>
+      <c r="D8">
         <v>13</v>
-      </c>
-      <c r="D8">
-        <v>11</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -956,11 +961,11 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
+        <v>12</v>
+      </c>
+      <c r="D9">
         <v>14</v>
-      </c>
-      <c r="D9">
-        <v>12</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -995,11 +1000,11 @@
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="8">
+        <v>13</v>
+      </c>
+      <c r="D10">
         <v>15</v>
-      </c>
-      <c r="D10">
-        <v>13</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -1031,11 +1036,11 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C11">
+      <c r="C11" s="8">
+        <v>13</v>
+      </c>
+      <c r="D11">
         <v>16</v>
-      </c>
-      <c r="D11">
-        <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>8</v>
@@ -1055,11 +1060,11 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C12">
+      <c r="C12" s="8">
+        <v>14</v>
+      </c>
+      <c r="D12">
         <v>17</v>
-      </c>
-      <c r="D12">
-        <v>14</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -1091,11 +1096,11 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C13">
+      <c r="C13" s="8">
+        <v>15</v>
+      </c>
+      <c r="D13">
         <v>18</v>
-      </c>
-      <c r="D13">
-        <v>15</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
